--- a/commissioning of temperature cabinets/IO_Schedule.xlsx
+++ b/commissioning of temperature cabinets/IO_Schedule.xlsx
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Pneumtic Open Position</t>
+          <t>Pneumatic Open Position (MOVED TO EL1859 DI 2)</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Pneumtic Close Position</t>
+          <t>Pneumatic Close Position (MOVED TO EL1859 DI 3)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-Stop </t>
+          <t>E-Stop (MOVED TO EL1859 DI 4)</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>Pneumatic Open Position</t>
         </is>
       </c>
       <c r="E12" s="1" t="n"/>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Spare</t>
+          <t>Pneumatic Close Position</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -4487,10 +4487,14 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Spare</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="n"/>
+          <t>E-Stop</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="n">
@@ -4498,7 +4502,7 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>DI 5</t>
+          <t>DI 4</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
@@ -4514,7 +4518,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>DI 6</t>
+          <t>DI 5</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -4530,7 +4534,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>DI 7</t>
+          <t>DI 6</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -4546,7 +4550,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>DI 8</t>
+          <t>DI 7</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">

--- a/commissioning of temperature cabinets/IO_Schedule.xlsx
+++ b/commissioning of temperature cabinets/IO_Schedule.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="2" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="ELM3148" sheetId="1" state="visible" r:id="rId1"/>
@@ -182,18 +182,21 @@
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -202,9 +205,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -609,18 +609,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.44140625" customWidth="1" style="5" min="2" max="2"/>
-    <col width="9.6640625" customWidth="1" style="5" min="3" max="3"/>
-    <col width="38.5546875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="10.88671875" bestFit="1" customWidth="1" style="5" min="6" max="6"/>
-    <col width="12.44140625" customWidth="1" style="5" min="7" max="7"/>
+    <col width="8.42578125" customWidth="1" style="6" min="2" max="2"/>
+    <col width="9.7109375" customWidth="1" style="6" min="3" max="3"/>
+    <col width="38.5703125" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="10.85546875" bestFit="1" customWidth="1" style="6" min="6" max="6"/>
+    <col width="12.42578125" customWidth="1" style="6" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Analog Inputs</t>
         </is>
@@ -631,7 +631,7 @@
       <c r="F2" s="1" t="n"/>
       <c r="G2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -663,7 +663,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
@@ -689,7 +689,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>1</v>
       </c>
@@ -715,7 +715,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
@@ -741,7 +741,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>1</v>
       </c>
@@ -767,7 +767,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
@@ -793,7 +793,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B9" s="1" t="n">
         <v>1</v>
       </c>
@@ -819,7 +819,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B10" s="1" t="n">
         <v>1</v>
       </c>
@@ -845,7 +845,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
@@ -871,8 +871,8 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="13" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="13" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B13" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -904,7 +904,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="14" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B14" s="1" t="n">
         <v>2</v>
       </c>
@@ -930,7 +930,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B15" s="1" t="n">
         <v>2</v>
       </c>
@@ -956,7 +956,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B16" s="1" t="n">
         <v>2</v>
       </c>
@@ -982,7 +982,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B17" s="1" t="n">
         <v>2</v>
       </c>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="18" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B18" s="1" t="n">
         <v>2</v>
       </c>
@@ -1034,7 +1034,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="19" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B19" s="1" t="n">
         <v>2</v>
       </c>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="20" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B20" s="1" t="n">
         <v>2</v>
       </c>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="21" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B21" s="1" t="n">
         <v>2</v>
       </c>
@@ -1127,14 +1127,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.88671875" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="27" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="24.5546875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="32.85546875" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
+    <col width="27" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="24.5703125" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Pin</t>
@@ -1161,11 +1161,11 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1174,7 +1174,7 @@
       <c r="D2" s="12" t="n"/>
       <c r="E2" s="11" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="E3" s="1" t="n"/>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E4" s="1" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="E5" s="1" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E6" s="1" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -1275,7 +1275,7 @@
       <c r="D7" s="1" t="n"/>
       <c r="E7" s="1" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
@@ -1292,7 +1292,7 @@
       <c r="D8" s="1" t="n"/>
       <c r="E8" s="1" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
@@ -1309,7 +1309,7 @@
       <c r="D9" s="1" t="n"/>
       <c r="E9" s="1" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
@@ -1326,11 +1326,11 @@
       <c r="D10" s="1" t="n"/>
       <c r="E10" s="1" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1339,7 +1339,7 @@
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
@@ -1356,7 +1356,7 @@
       <c r="D12" s="1" t="n"/>
       <c r="E12" s="1" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
@@ -1373,7 +1373,7 @@
       <c r="D13" s="1" t="n"/>
       <c r="E13" s="1" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="14" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
@@ -1423,7 +1423,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
@@ -1448,7 +1448,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
@@ -1465,7 +1465,7 @@
       <c r="D17" s="1" t="n"/>
       <c r="E17" s="1" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="18" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
@@ -1482,7 +1482,7 @@
       <c r="D18" s="1" t="n"/>
       <c r="E18" s="1" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="19" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
@@ -1499,11 +1499,11 @@
       <c r="D19" s="1" t="n"/>
       <c r="E19" s="1" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="20" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1512,11 +1512,11 @@
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="11" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="21" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1525,7 +1525,7 @@
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="11" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="22" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="23" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="24" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="25" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="26" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="27" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
@@ -1651,7 +1651,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="28" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="29" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
@@ -1693,11 +1693,11 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="30" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -1706,7 +1706,7 @@
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="11" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="31" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="32" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="33" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="34" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="35" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="36" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="37" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="38" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
@@ -1893,16 +1893,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7.109375" customWidth="1" style="5" min="1" max="1"/>
-    <col width="8.5546875" bestFit="1" customWidth="1" style="5" min="2" max="2"/>
-    <col width="51" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="14" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="23.33203125" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="7.140625" customWidth="1" style="6" min="1" max="1"/>
+    <col width="8.5703125" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
+    <col width="51" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
+    <col width="14" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="23.28515625" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Pin</t>
@@ -1934,11 +1934,11 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -1948,7 +1948,7 @@
       <c r="E2" s="12" t="n"/>
       <c r="F2" s="11" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
@@ -1996,7 +1996,7 @@
       <c r="E4" s="1" t="n"/>
       <c r="F4" s="13" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
@@ -2016,13 +2016,13 @@
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
@@ -2044,7 +2044,7 @@
       <c r="E6" s="1" t="n"/>
       <c r="F6" s="13" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
@@ -2064,13 +2064,13 @@
         </is>
       </c>
       <c r="E7" s="1" t="n"/>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>1-5V</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
@@ -2092,7 +2092,7 @@
       <c r="E8" s="1" t="n"/>
       <c r="F8" s="13" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
@@ -2112,13 +2112,13 @@
         </is>
       </c>
       <c r="E9" s="1" t="n"/>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
@@ -2140,11 +2140,11 @@
       <c r="E10" s="1" t="n"/>
       <c r="F10" s="13" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2154,7 +2154,7 @@
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="11" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="E12" s="1" t="n"/>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
@@ -2202,7 +2202,7 @@
       <c r="E13" s="1" t="n"/>
       <c r="F13" s="13" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="14" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
@@ -2222,13 +2222,13 @@
         </is>
       </c>
       <c r="E14" s="1" t="n"/>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="E15" s="1" t="n"/>
       <c r="F15" s="13" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
@@ -2270,13 +2270,13 @@
         </is>
       </c>
       <c r="E16" s="1" t="n"/>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="E17" s="1" t="n"/>
       <c r="F17" s="13" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="18" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
@@ -2318,13 +2318,13 @@
         </is>
       </c>
       <c r="E18" s="1" t="n"/>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="19" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
@@ -2346,11 +2346,11 @@
       <c r="E19" s="1" t="n"/>
       <c r="F19" s="13" t="n"/>
     </row>
-    <row r="20" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="20" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
@@ -2360,11 +2360,11 @@
       <c r="E20" s="12" t="n"/>
       <c r="F20" s="11" t="n"/>
     </row>
-    <row r="21" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="21" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2374,7 +2374,7 @@
       <c r="E21" s="12" t="n"/>
       <c r="F21" s="11" t="n"/>
     </row>
-    <row r="22" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="22" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="E22" s="1" t="n"/>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>4-20mA</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="23" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
@@ -2422,7 +2422,7 @@
       <c r="E23" s="1" t="n"/>
       <c r="F23" s="13" t="n"/>
     </row>
-    <row r="24" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="24" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A24" s="1" t="n">
         <v>23</v>
       </c>
@@ -2438,9 +2438,9 @@
       </c>
       <c r="D24" s="1" t="n"/>
       <c r="E24" s="1" t="n"/>
-      <c r="F24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="5" thickBot="1">
+      <c r="F24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A25" s="1" t="n">
         <v>24</v>
       </c>
@@ -2458,7 +2458,7 @@
       <c r="E25" s="1" t="n"/>
       <c r="F25" s="13" t="n"/>
     </row>
-    <row r="26" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="26" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A26" s="1" t="n">
         <v>25</v>
       </c>
@@ -2478,13 +2478,13 @@
         </is>
       </c>
       <c r="E26" s="1" t="n"/>
-      <c r="F26" s="10" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>RGBW</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="27" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A27" s="1" t="n">
         <v>26</v>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="E27" s="1" t="n"/>
       <c r="F27" s="14" t="n"/>
     </row>
-    <row r="28" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="28" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A28" s="1" t="n">
         <v>27</v>
       </c>
@@ -2528,7 +2528,7 @@
       <c r="E28" s="1" t="n"/>
       <c r="F28" s="14" t="n"/>
     </row>
-    <row r="29" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="29" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A29" s="1" t="n">
         <v>28</v>
       </c>
@@ -2550,11 +2550,11 @@
       <c r="E29" s="1" t="n"/>
       <c r="F29" s="13" t="n"/>
     </row>
-    <row r="30" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="30" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A30" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
@@ -2564,7 +2564,7 @@
       <c r="E30" s="12" t="n"/>
       <c r="F30" s="11" t="n"/>
     </row>
-    <row r="31" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="31" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A31" s="1" t="n">
         <v>30</v>
       </c>
@@ -2586,7 +2586,7 @@
       <c r="E31" s="1" t="n"/>
       <c r="F31" s="1" t="n"/>
     </row>
-    <row r="32" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="32" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A32" s="1" t="n">
         <v>31</v>
       </c>
@@ -2604,7 +2604,7 @@
       <c r="E32" s="1" t="n"/>
       <c r="F32" s="1" t="n"/>
     </row>
-    <row r="33" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="33" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A33" s="1" t="n">
         <v>32</v>
       </c>
@@ -2622,7 +2622,7 @@
       <c r="E33" s="1" t="n"/>
       <c r="F33" s="1" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="34" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A34" s="1" t="n">
         <v>33</v>
       </c>
@@ -2640,7 +2640,7 @@
       <c r="E34" s="1" t="n"/>
       <c r="F34" s="1" t="n"/>
     </row>
-    <row r="35" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="35" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A35" s="1" t="n">
         <v>34</v>
       </c>
@@ -2658,7 +2658,7 @@
       <c r="E35" s="1" t="n"/>
       <c r="F35" s="1" t="n"/>
     </row>
-    <row r="36" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="36" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A36" s="1" t="n">
         <v>35</v>
       </c>
@@ -2676,7 +2676,7 @@
       <c r="E36" s="1" t="n"/>
       <c r="F36" s="1" t="n"/>
     </row>
-    <row r="37" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="37" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A37" s="1" t="n">
         <v>36</v>
       </c>
@@ -2694,7 +2694,7 @@
       <c r="E37" s="1" t="n"/>
       <c r="F37" s="1" t="n"/>
     </row>
-    <row r="38" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="38" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A38" s="1" t="n">
         <v>37</v>
       </c>
@@ -2721,10 +2721,10 @@
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="B21:F21"/>
+    <mergeCell ref="F26:F29"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="F22:F23"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="F22:F23"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="B30:F30"/>
@@ -2746,17 +2746,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.44140625" customWidth="1" style="5" min="2" max="2"/>
-    <col width="9.5546875" customWidth="1" style="5" min="3" max="3"/>
-    <col width="38.5546875" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="10.88671875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="10.42578125" customWidth="1" style="6" min="2" max="2"/>
+    <col width="9.5703125" customWidth="1" style="6" min="3" max="3"/>
+    <col width="38.5703125" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="10.85546875" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Thermocouple Inputs</t>
         </is>
@@ -2765,7 +2765,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>3</v>
       </c>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>3</v>
       </c>
@@ -2874,15 +2874,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34.44140625" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="12" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="34.42578125" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Digital Output</t>
         </is>
@@ -2891,7 +2891,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>4</v>
       </c>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>4</v>
       </c>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>4</v>
       </c>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B8" s="1" t="n">
         <v>4</v>
       </c>
@@ -3003,7 +3003,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B9" s="1" t="n">
         <v>4</v>
       </c>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B10" s="1" t="n">
         <v>4</v>
       </c>
@@ -3039,7 +3039,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B11" s="1" t="n">
         <v>4</v>
       </c>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B12" s="1" t="n">
         <v>4</v>
       </c>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="E12" s="1" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B13" s="1" t="n">
         <v>4</v>
       </c>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="E13" s="1" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="14" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B14" s="1" t="n">
         <v>4</v>
       </c>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B15" s="1" t="n">
         <v>4</v>
       </c>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B16" s="1" t="n">
         <v>4</v>
       </c>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B17" s="1" t="n">
         <v>4</v>
       </c>
@@ -3157,7 +3157,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="18" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B18" s="1" t="n">
         <v>4</v>
       </c>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="19" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B19" s="1" t="n">
         <v>4</v>
       </c>
@@ -3204,15 +3204,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34.44140625" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="12" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="34.42578125" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Digital Output</t>
         </is>
@@ -3221,7 +3221,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="E4" s="1" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>5</v>
       </c>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="E5" s="1" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="E6" s="1" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>5</v>
       </c>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="E7" s="1" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B8" s="1" t="n">
         <v>5</v>
       </c>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="E8" s="1" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B9" s="1" t="n">
         <v>5</v>
       </c>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="E9" s="1" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B10" s="1" t="n">
         <v>5</v>
       </c>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="E10" s="1" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B11" s="1" t="n">
         <v>5</v>
       </c>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="E11" s="1" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B12" s="1" t="n">
         <v>5</v>
       </c>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="E12" s="1" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="E13" s="1" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="14" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B14" s="1" t="n">
         <v>5</v>
       </c>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="E14" s="1" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B15" s="1" t="n">
         <v>5</v>
       </c>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E15" s="1" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B16" s="1" t="n">
         <v>5</v>
       </c>
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E16" s="1" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B17" s="1" t="n">
         <v>5</v>
       </c>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="E17" s="1" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="18" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B18" s="1" t="n">
         <v>5</v>
       </c>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="E18" s="1" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="19" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B19" s="1" t="n">
         <v>5</v>
       </c>
@@ -3482,18 +3482,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="5" min="1" max="1"/>
-    <col width="13" customWidth="1" style="5" min="2" max="2"/>
-    <col width="13" customWidth="1" style="5" min="3" max="3"/>
-    <col width="23.44140625" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="12" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Digital Inputs</t>
         </is>
@@ -3502,7 +3499,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -3524,7 +3521,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>6</v>
       </c>
@@ -3538,7 +3535,7 @@
       </c>
       <c r="E4" s="1" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>6</v>
       </c>
@@ -3552,7 +3549,7 @@
       </c>
       <c r="E5" s="1" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>6</v>
       </c>
@@ -3570,7 +3567,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
@@ -3584,7 +3581,7 @@
       </c>
       <c r="E7" s="1" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B8" s="1" t="n">
         <v>6</v>
       </c>
@@ -3598,7 +3595,7 @@
       </c>
       <c r="E8" s="1" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B9" s="1" t="n">
         <v>6</v>
       </c>
@@ -3612,7 +3609,7 @@
       </c>
       <c r="E9" s="1" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B10" s="1" t="n">
         <v>6</v>
       </c>
@@ -3626,7 +3623,7 @@
       </c>
       <c r="E10" s="1" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B11" s="1" t="n">
         <v>6</v>
       </c>
@@ -3640,7 +3637,7 @@
       </c>
       <c r="E11" s="1" t="n"/>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="12" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B12" s="1" t="n">
         <v>6</v>
       </c>
@@ -3654,7 +3651,7 @@
       </c>
       <c r="E12" s="1" t="n"/>
     </row>
-    <row r="13" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="13" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B13" s="1" t="n">
         <v>6</v>
       </c>
@@ -3668,7 +3665,7 @@
       </c>
       <c r="E13" s="1" t="n"/>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="14" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B14" s="1" t="n">
         <v>6</v>
       </c>
@@ -3682,7 +3679,7 @@
       </c>
       <c r="E14" s="1" t="n"/>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="15" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B15" s="1" t="n">
         <v>6</v>
       </c>
@@ -3696,7 +3693,7 @@
       </c>
       <c r="E15" s="1" t="n"/>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="16" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B16" s="1" t="n">
         <v>6</v>
       </c>
@@ -3710,7 +3707,7 @@
       </c>
       <c r="E16" s="1" t="n"/>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="17" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B17" s="1" t="n">
         <v>6</v>
       </c>
@@ -3724,7 +3721,7 @@
       </c>
       <c r="E17" s="1" t="n"/>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="18" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B18" s="1" t="n">
         <v>6</v>
       </c>
@@ -3738,7 +3735,7 @@
       </c>
       <c r="E18" s="1" t="n"/>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="19" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B19" s="1" t="n">
         <v>6</v>
       </c>
@@ -3767,16 +3764,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.33203125" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="47.109375" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="12" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="8.28515625" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
+    <col width="47.140625" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Analog Output</t>
         </is>
@@ -3785,7 +3782,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -3807,7 +3804,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>7</v>
       </c>
@@ -3825,7 +3822,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>7</v>
       </c>
@@ -3843,7 +3840,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>7</v>
       </c>
@@ -3861,7 +3858,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>7</v>
       </c>
@@ -3879,7 +3876,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
@@ -3897,7 +3894,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B9" s="1" t="n">
         <v>7</v>
       </c>
@@ -3915,7 +3912,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B10" s="1" t="n">
         <v>7</v>
       </c>
@@ -3933,7 +3930,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B11" s="1" t="n">
         <v>7</v>
       </c>
@@ -3966,16 +3963,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" style="5" min="3" max="3"/>
-    <col width="50" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="10.88671875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="9" customWidth="1" style="6" min="3" max="3"/>
+    <col width="50" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="10.85546875" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Analog Output</t>
         </is>
@@ -3984,7 +3981,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -4006,7 +4003,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>8</v>
       </c>
@@ -4024,7 +4021,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>8</v>
       </c>
@@ -4038,7 +4035,7 @@
       </c>
       <c r="E5" s="1" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>8</v>
       </c>
@@ -4052,7 +4049,7 @@
       </c>
       <c r="E6" s="1" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>8</v>
       </c>
@@ -4066,7 +4063,7 @@
       </c>
       <c r="E7" s="1" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="8" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B8" s="1" t="n">
         <v>8</v>
       </c>
@@ -4080,7 +4077,7 @@
       </c>
       <c r="E8" s="1" t="n"/>
     </row>
-    <row r="9" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="9" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
@@ -4094,7 +4091,7 @@
       </c>
       <c r="E9" s="1" t="n"/>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="10" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B10" s="1" t="n">
         <v>8</v>
       </c>
@@ -4108,7 +4105,7 @@
       </c>
       <c r="E10" s="1" t="n"/>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="11" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B11" s="1" t="n">
         <v>8</v>
       </c>
@@ -4140,15 +4137,15 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40.109375" bestFit="1" customWidth="1" style="5" min="4" max="4"/>
-    <col width="10.88671875" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
+    <col width="40.140625" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
+    <col width="10.85546875" bestFit="1" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5" thickBot="1"/>
-    <row r="2" ht="15" customHeight="1" s="5" thickBot="1">
-      <c r="B2" s="2" t="inlineStr">
+    <row r="1" ht="15.75" customHeight="1" s="6" thickBot="1"/>
+    <row r="2" ht="15.75" customHeight="1" s="6" thickBot="1">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>RGBW</t>
         </is>
@@ -4157,7 +4154,7 @@
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="3" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
@@ -4179,7 +4176,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="4" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B4" s="1" t="n">
         <v>9</v>
       </c>
@@ -4193,7 +4190,7 @@
       </c>
       <c r="E4" s="1" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="5" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B5" s="1" t="n">
         <v>9</v>
       </c>
@@ -4207,7 +4204,7 @@
       </c>
       <c r="E5" s="1" t="n"/>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="6" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B6" s="1" t="n">
         <v>9</v>
       </c>
@@ -4221,7 +4218,7 @@
       </c>
       <c r="E6" s="1" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5" thickBot="1">
+    <row r="7" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="B7" s="1" t="n">
         <v>9</v>
       </c>
@@ -4249,62 +4246,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E18"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="5" min="1" max="1"/>
-    <col width="13" customWidth="1" style="5" min="2" max="2"/>
-    <col width="13" customWidth="1" style="5" min="3" max="3"/>
-    <col width="23.44140625" customWidth="1" style="5" min="4" max="4"/>
-    <col width="12" customWidth="1" style="5" min="5" max="5"/>
+    <col width="46" customWidth="1" style="6" min="4" max="4"/>
+    <col width="12" customWidth="1" style="6" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" t="inlineStr">
+    <row r="2">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Digital Input / Output Combi</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>Channel</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>Default State</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>DO 1</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Temp Cab Start (Relay 1 coil) - 37way pin 13</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Off</t>
         </is>
       </c>
     </row>
@@ -4314,12 +4291,12 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>DO 2</t>
+          <t>DO 1</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Temp Cab Stop (Relay 2 coil) - 37way pin 14</t>
+          <t>Temp Cab Start (Relay 1 coil) - 37way pin 13</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
@@ -4334,15 +4311,19 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>DO 3</t>
+          <t>DO 2</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Spare</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n"/>
+          <t>Temp Cab Stop (Relay 2 coil) - 37way pin 14</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="n">
@@ -4350,7 +4331,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>DO 4</t>
+          <t>DO 3</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -4366,7 +4347,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>DO 5</t>
+          <t>DO 4</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -4382,7 +4363,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>DO 6</t>
+          <t>DO 5</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -4398,7 +4379,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>DO 7</t>
+          <t>DO 6</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -4414,7 +4395,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>DO 8</t>
+          <t>DO 7</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -4430,19 +4411,15 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>DI 1</t>
+          <t>DO 8</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>Temp Cab Run Feedback (latch aux) - 37way pin 15</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+          <t>Spare</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="1" t="n">
@@ -4450,15 +4427,19 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>DI 2</t>
+          <t>DI 1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Pneumatic Open Position</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n"/>
+          <t>Temp Cab Run Feedback (latch aux) - 37way pin 15</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="1" t="n">
@@ -4466,12 +4447,12 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>DI 3</t>
+          <t>DI 2</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Pneumatic Close Position</t>
+          <t>Pneumatic Open Position (from EL1409 ch 1)</t>
         </is>
       </c>
       <c r="E13" s="1" t="n"/>
@@ -4482,19 +4463,15 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>DI 4</t>
+          <t>DI 3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>E-Stop</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>Pneumatic Close Position (from EL1409 ch 2)</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="1" t="n">
@@ -4507,10 +4484,14 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Spare</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n"/>
+          <t>E-Stop (from EL1409 ch 3)</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="1" t="n">
@@ -4560,7 +4541,26 @@
       </c>
       <c r="E18" s="1" t="n"/>
     </row>
+    <row r="19">
+      <c r="B19" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>DI 8</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>Spare</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/commissioning of temperature cabinets/IO_Schedule.xlsx
+++ b/commissioning of temperature cabinets/IO_Schedule.xlsx
@@ -1434,19 +1434,11 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>Temp Cab Run Feedback</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>Temp Cab - all</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>DLS.GVL_HMI.xCabinetRunFb</t>
-        </is>
-      </c>
+          <t>DI Spare 12</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="6" thickBot="1">
       <c r="A17" s="1" t="n">
@@ -4432,14 +4424,10 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Temp Cab Run Feedback (latch aux) - 37way pin 15</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
+          <t>Spare</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="1" t="n">

--- a/commissioning of temperature cabinets/IO_Schedule.xlsx
+++ b/commissioning of temperature cabinets/IO_Schedule.xlsx
@@ -3473,7 +3473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E19"/>
+  <dimension ref="A2:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.42578125" bestFit="1" customWidth="1" style="6" min="4" max="4"/>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Pneumatic Open Position (MOVED TO EL1859 DI 2)</t>
+          <t>Pneumatic Open Position (MOVED TO EL1859 DI 1)</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Pneumatic Close Position (MOVED TO EL1859 DI 3)</t>
+          <t>Pneumatic Close Position (MOVED TO EL1859 DI 2)</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>E-Stop (MOVED TO EL1859 DI 4)</t>
+          <t>E-Stop (MOVED TO EL1859 DI 3)</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
@@ -4283,19 +4283,15 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>DO 1</t>
+          <t>DI 1</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>Temp Cab Start (Relay 1 coil) - 37way pin 13</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
+          <t>Pneumatic Open Position (from EL1409 ch 1)</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="1" t="n">
@@ -4303,19 +4299,15 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>DO 2</t>
+          <t>DI 2</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>Temp Cab Stop (Relay 2 coil) - 37way pin 14</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Off</t>
-        </is>
-      </c>
+          <t>Pneumatic Close Position (from EL1409 ch 2)</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="1" t="n">
@@ -4323,15 +4315,19 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>DO 3</t>
+          <t>DI 3</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>Spare</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n"/>
+          <t>E-Stop (from EL1409 ch 3)</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="n">
@@ -4339,7 +4335,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>DO 4</t>
+          <t>DI 4</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -4355,7 +4351,7 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>DO 5</t>
+          <t>DI 5</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
@@ -4371,7 +4367,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>DO 6</t>
+          <t>DI 6</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -4387,7 +4383,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>DO 7</t>
+          <t>DI 7</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
@@ -4403,7 +4399,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>DO 8</t>
+          <t>DI 8</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
@@ -4419,15 +4415,19 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>DI 1</t>
+          <t>DO 1</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>Spare</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="n"/>
+          <t>Temp Cab Start (Relay 1 coil) - 37way pin 13</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="1" t="n">
@@ -4435,15 +4435,19 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>DI 2</t>
+          <t>DO 2</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>Pneumatic Open Position (from EL1409 ch 1)</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="n"/>
+          <t>Temp Cab Stop (Relay 2 coil) - 37way pin 14</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Off</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="n">
@@ -4451,12 +4455,12 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>DI 3</t>
+          <t>DO 3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>Pneumatic Close Position (from EL1409 ch 2)</t>
+          <t>Spare</t>
         </is>
       </c>
       <c r="E14" s="1" t="n"/>
@@ -4467,19 +4471,15 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>DI 4</t>
+          <t>DO 4</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>E-Stop (from EL1409 ch 3)</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+          <t>Spare</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="1" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>DI 5</t>
+          <t>DO 5</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>DI 6</t>
+          <t>DO 6</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>DI 7</t>
+          <t>DO 7</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>DI 8</t>
+          <t>DO 8</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
